--- a/reports/pdf_change_20261008.xlsx
+++ b/reports/pdf_change_20261008.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,416억   ·   현금 1억(0.0%)      당일 2026-10-08  vs  전영업일 2026-10-07      매수 5종목  /  매도 6종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,326억      당일 2026-10-08  vs  전영업일 2026-10-07      매수 5종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>105</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1595412688</v>
+        <v>1606877574</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-219</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2418891083</v>
+        <v>-2436273614</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>29</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1587425885</v>
+        <v>1598833376</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-46</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1462851231</v>
+        <v>-1473363510</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>28</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>552258238</v>
+        <v>556226853</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-15</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-956955413</v>
+        <v>-963832245</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>27</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1044031050</v>
+        <v>1051533621</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-7</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-490896212</v>
+        <v>-494423869</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>19</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1576711880</v>
+        <v>1588042379</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-6</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-139379460</v>
+        <v>-140381063</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>-5</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-246909106</v>
+        <v>-248683434</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,499억   ·   현금 27억(0.8%)      당일 2026-10-08  vs  전영업일 2026-10-07      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,467억      당일 2026-10-08  vs  전영업일 2026-10-07      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -935,7 +935,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,947억   ·   현금 41억(1.5%)      당일 2026-10-08  vs  전영업일 2026-10-07      매수 1종목  /  매도 2종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,834억      당일 2026-10-08  vs  전영업일 2026-10-07      매수 1종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -1031,7 +1031,7 @@
         <v>10</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>2095081138</v>
+        <v>2101400695</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>-197</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-1290437381</v>
+        <v>-1294329828</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>-26</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1251479480</v>
+        <v>-1255254415</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,198억   ·   현금 8억(0.4%)      당일 2026-10-08  vs  전영업일 2026-10-07      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,225억      당일 2026-10-08  vs  전영업일 2026-10-07      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1120,7 +1120,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 325억   ·   현금 3억(0.8%)      당일 2026-10-08  vs  전영업일 2026-10-07      매수 1종목  /  매도 4종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 315억      당일 2026-10-08  vs  전영업일 2026-10-07      매수 1종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1216,7 +1216,7 @@
         <v>89</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>95500560</v>
+        <v>94411172</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1237,11 +1237,11 @@
         <v>-60</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-61281600</v>
+        <v>-58343983</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>0.70%→0.51%</t>
+          <t>0.68%→0.50%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
@@ -1265,11 +1265,11 @@
         <v>-44</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-36143360</v>
+        <v>-35544950</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>1.61%→1.51%</t>
+          <t>1.64%→1.53%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
@@ -1293,11 +1293,11 @@
         <v>-17</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-31269800</v>
+        <v>-30055991</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>4.95%→4.86%</t>
+          <t>4.91%→4.82%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
@@ -1321,11 +1321,11 @@
         <v>-10</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-63920000</v>
+        <v>-64395981</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>1.19%→0.99%</t>
+          <t>1.23%→1.03%</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
